--- a/school_surveys/021_student_retention_survey--school_surveys.xlsx
+++ b/school_surveys/021_student_retention_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Student ID</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter student ID</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -551,7 +555,11 @@
           <t>Teacher Name</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter teacher name</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -571,7 +579,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>student_reasons_left</t>
+          <t>Reasons for Students Leaving</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +602,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Other Reasons for Leaving</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teacher_reasons_left</t>
+          <t>Reasons for Teachers Leaving</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +648,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Other Reasons for Teachers Leaving</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +671,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>teacher_support</t>
+          <t>Teacher Support Systems</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,10 +694,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Other Teacher Support System</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please specify the other teacher support system</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -709,10 +721,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>student_support</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Student Support Systems</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Student Support Systems</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -732,10 +748,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Other Student Support System</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please specify the other student support system</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -755,10 +775,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>teacher_comments</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Teacher Comments</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide comments</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -778,10 +802,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>student_comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Student Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide comments</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -801,10 +829,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>school_id</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>School ID</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter school ID</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -824,10 +856,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>grade_level</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Grade Level</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter grade level</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -847,10 +883,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>student_retention_date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Student Retention Date</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please select the date of student retention</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>yes</t>
@@ -870,10 +910,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>teacher_survey_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Teacher Survey Date</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please select the date of teacher survey</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>yes</t>
@@ -891,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1077,29 +1121,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>teacher_support_choices</t>
+          <t>student_support_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1111,27 +1155,10 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>student_support_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
